--- a/โจทย์.xlsx
+++ b/โจทย์.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\trianing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\training\training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C34B754-C198-4990-B14F-A7310675EEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0E26EE-0D9A-4158-BF68-483F94CE75A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CAB351B-968C-4316-853A-F221F58B3487}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
   <si>
     <t>โจทย์</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>ตัวเลือกที่ถูกต้อง</t>
+  </si>
+  <si>
+    <t>โจทย์ 11</t>
+  </si>
+  <si>
+    <t>โจทย์ 12</t>
   </si>
 </sst>
 </file>
@@ -448,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7EEACC9-B181-4BA7-B2C4-A55DE069F967}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -717,6 +723,52 @@
         <v>2</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>

--- a/โจทย์.xlsx
+++ b/โจทย์.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\training\training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0E26EE-0D9A-4158-BF68-483F94CE75A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83940FE0-FD7C-4C73-8A58-4C4F1975BC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CAB351B-968C-4316-853A-F221F58B3487}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="21">
   <si>
     <t>โจทย์</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>โจทย์ 12</t>
+  </si>
+  <si>
+    <t>โจทย์ 13</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7EEACC9-B181-4BA7-B2C4-A55DE069F967}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -769,6 +772,29 @@
         <v>2</v>
       </c>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>

--- a/โจทย์.xlsx
+++ b/โจทย์.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\training\training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83940FE0-FD7C-4C73-8A58-4C4F1975BC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790B6E8C-FCF8-4391-BCF0-6C7CB2457368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CAB351B-968C-4316-853A-F221F58B3487}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="18">
   <si>
     <t>โจทย์</t>
   </si>
@@ -86,15 +86,6 @@
   </si>
   <si>
     <t>ตัวเลือกที่ถูกต้อง</t>
-  </si>
-  <si>
-    <t>โจทย์ 11</t>
-  </si>
-  <si>
-    <t>โจทย์ 12</t>
-  </si>
-  <si>
-    <t>โจทย์ 13</t>
   </si>
 </sst>
 </file>
@@ -457,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7EEACC9-B181-4BA7-B2C4-A55DE069F967}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -726,75 +717,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
